--- a/projeto/Backlog.xlsx
+++ b/projeto/Backlog.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\MeusProjetosProgramacao\processo-man\projeto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F3E8C8-E1EB-4EEF-9C84-F5090D788723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDAA151-B065-48E9-8B4F-31F29C27A7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24210" yWindow="0" windowWidth="14295" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="requisitos" sheetId="1" r:id="rId1"/>
-    <sheet name="telas" sheetId="3" r:id="rId2"/>
+    <sheet name="requisitos" sheetId="3" r:id="rId1"/>
+    <sheet name="tarefas" sheetId="1" r:id="rId2"/>
     <sheet name="revisões" sheetId="4" r:id="rId3"/>
     <sheet name="variaveis" sheetId="2" r:id="rId4"/>
   </sheets>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
   <si>
     <t>Status</t>
   </si>
@@ -244,12 +244,66 @@
   </si>
   <si>
     <t>RNF</t>
+  </si>
+  <si>
+    <t>requisito</t>
+  </si>
+  <si>
+    <t>modulo</t>
+  </si>
+  <si>
+    <t>secretaria</t>
+  </si>
+  <si>
+    <t>situação</t>
+  </si>
+  <si>
+    <t>cadastrar um processo</t>
+  </si>
+  <si>
+    <t>cadastrar um cliente</t>
+  </si>
+  <si>
+    <t>editar um processo</t>
+  </si>
+  <si>
+    <t>editar um cliente</t>
+  </si>
+  <si>
+    <t>listar processos</t>
+  </si>
+  <si>
+    <t>listar clientes</t>
+  </si>
+  <si>
+    <t>especificação</t>
+  </si>
+  <si>
+    <t>área secretaria</t>
+  </si>
+  <si>
+    <t>detalhes de um cliente</t>
+  </si>
+  <si>
+    <t>detalhes de um processo</t>
+  </si>
+  <si>
+    <t>editar o cliente</t>
+  </si>
+  <si>
+    <t>editar o processo</t>
+  </si>
+  <si>
+    <t>listar processos do cliente</t>
+  </si>
+  <si>
+    <t>ator</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -279,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -293,19 +347,126 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+  <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="medium">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+        <vertical style="hair">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </vertical>
+        <horizontal style="double">
+          <color theme="0"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="5" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -318,86 +479,36 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="5" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="5" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="Estilo de Tabela 1" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Estilo de Tabela 1" pivot="0" count="2" xr9:uid="{2857735E-9015-42FE-A372-C53B872E8FB9}">
+      <tableStyleElement type="wholeTable" dxfId="5"/>
+      <tableStyleElement type="headerRow" dxfId="4"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -410,19 +521,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EA8F9240-8153-43D4-87B0-3D66E3B5AE69}" name="Tabela1" displayName="Tabela1" ref="A1:D34" totalsRowShown="0" headerRowDxfId="0" dataDxfId="13">
-  <autoFilter ref="A1:D34" xr:uid="{EA8F9240-8153-43D4-87B0-3D66E3B5AE69}">
-    <filterColumn colId="3">
-      <filters blank="1">
-        <filter val="Pendente"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8AA210AF-1D18-4837-8337-7E8DD18CFD82}" name="Tabela2" displayName="Tabela2" ref="A1:E12" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:E12" xr:uid="{8AA210AF-1D18-4837-8337-7E8DD18CFD82}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D3DBD901-6962-4639-9109-C1FA5F6829E0}" name="ator" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{CD4FFF46-5557-471C-B201-D0340224D495}" name="modulo" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{74832AAB-C227-450E-91A0-9754FD84CD2B}" name="requisito" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{CF530332-D6EF-43F6-8B7C-1E741395A17A}" name="especificação" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{8969C299-8531-4D08-924E-8F730122ED69}" name="situação" dataDxfId="6"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de Tabela 1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EA8F9240-8153-43D4-87B0-3D66E3B5AE69}" name="Tabela1" displayName="Tabela1" ref="A1:D34" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:D34" xr:uid="{EA8F9240-8153-43D4-87B0-3D66E3B5AE69}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{31454B32-4772-4261-8D8C-3A3154227916}" name="id" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{A09423A3-C512-413D-8A47-82400299741B}" name="Item / Módulo" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{9936F96F-D4F9-429E-92AD-185C72846981}" name="Descrição do Requisito" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{9B0F8BC4-636D-4B1E-A4A3-5B52F926492D}" name="Status" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{31454B32-4772-4261-8D8C-3A3154227916}" name="id" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{A09423A3-C512-413D-8A47-82400299741B}" name="Item / Módulo" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{9936F96F-D4F9-429E-92AD-185C72846981}" name="Descrição do Requisito" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{9B0F8BC4-636D-4B1E-A4A3-5B52F926492D}" name="Status" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -690,14 +809,236 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AB5BD8C-816E-4BA6-A9F5-911C687FAFCF}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="36" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="41.5703125" customWidth="1"/>
+    <col min="4" max="4" width="33.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:E12">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$E2="desenvolver"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$E2="feito"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{09EDA941-FD51-41B5-827D-5336B36C8955}">
+          <x14:formula1>
+            <xm:f>variaveis!$B$2:$B$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E12</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="77.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="38.5703125" customWidth="1"/>
+    <col min="3" max="3" width="80.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -714,7 +1055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>68</v>
       </c>
@@ -728,7 +1069,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>68</v>
       </c>
@@ -742,7 +1083,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>68</v>
       </c>
@@ -756,7 +1097,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>68</v>
       </c>
@@ -770,7 +1111,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>68</v>
       </c>
@@ -784,7 +1125,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>68</v>
       </c>
@@ -798,7 +1139,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>68</v>
       </c>
@@ -812,7 +1153,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>68</v>
       </c>
@@ -826,7 +1167,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>68</v>
       </c>
@@ -840,7 +1181,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>68</v>
       </c>
@@ -854,7 +1195,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>68</v>
       </c>
@@ -868,7 +1209,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>68</v>
       </c>
@@ -882,7 +1223,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>68</v>
       </c>
@@ -896,7 +1237,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>68</v>
       </c>
@@ -910,7 +1251,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>68</v>
       </c>
@@ -924,7 +1265,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>68</v>
       </c>
@@ -938,7 +1279,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>68</v>
       </c>
@@ -952,7 +1293,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>68</v>
       </c>
@@ -966,7 +1307,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>68</v>
       </c>
@@ -980,7 +1321,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>68</v>
       </c>
@@ -994,7 +1335,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
@@ -1008,7 +1349,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>68</v>
       </c>
@@ -1022,7 +1363,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>68</v>
       </c>
@@ -1036,7 +1377,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>68</v>
       </c>
@@ -1050,7 +1391,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>68</v>
       </c>
@@ -1064,7 +1405,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>68</v>
       </c>
@@ -1143,14 +1484,14 @@
   </sheetData>
   <dataConsolidate/>
   <conditionalFormatting sqref="A1:D34">
-    <cfRule type="expression" dxfId="5" priority="3">
-      <formula>$D1="Feito"</formula>
+    <cfRule type="expression" dxfId="13" priority="1">
+      <formula>$D1="Pendente"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>$D1="Desenvolver"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>$D1="Pendente"</formula>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>$D1="Feito"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1178,15 +1519,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AB5BD8C-816E-4BA6-A9F5-911C687FAFCF}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FCF0538-3CF2-47D2-8374-A1DB10778F8F}">
   <dimension ref="A1"/>

--- a/projeto/Backlog.xlsx
+++ b/projeto/Backlog.xlsx
@@ -1,20 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC4F626-80AA-498B-9CCD-44940DA076AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="1035" yWindow="0" windowWidth="29760" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="requisitos" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="tarefas" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="revisões" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="variaveis" state="visible" r:id="rId7"/>
+    <sheet name="tarefas" sheetId="2" r:id="rId1"/>
+    <sheet name="requisitos" sheetId="1" r:id="rId2"/>
+    <sheet name="variaveis" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="103">
   <si>
     <t>ator</t>
   </si>
@@ -293,26 +309,63 @@
   </si>
   <si>
     <t>RNF</t>
+  </si>
+  <si>
+    <t>aberto</t>
+  </si>
+  <si>
+    <t>tela de detalhes do usuario</t>
+  </si>
+  <si>
+    <t>um processo poder ser atribuido a vários clientes</t>
+  </si>
+  <si>
+    <t>regra de negocio</t>
+  </si>
+  <si>
+    <t>imagem rev01
+listar os processos vinculados ao usuario, tanto como responsável como dono</t>
+  </si>
+  <si>
+    <t>tela lista de colaboradores</t>
+  </si>
+  <si>
+    <t>imagem rev02
+botão para listar os processos do colaboradoir</t>
+  </si>
+  <si>
+    <t>elaborar front end react</t>
+  </si>
+  <si>
+    <t>criar apis par ao front react</t>
+  </si>
+  <si>
+    <t>componentizar os views templates html</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,11 +374,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF843C0A"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -333,15 +393,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -349,12 +421,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -363,12 +432,173 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -379,6 +609,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2A3BB3FF-74DB-4126-ACB2-D1315D2CA9CA}" name="Tabela1" displayName="Tabela1" ref="A1:D38" totalsRowShown="0">
+  <autoFilter ref="A1:D38" xr:uid="{2A3BB3FF-74DB-4126-ACB2-D1315D2CA9CA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D34">
+    <sortCondition ref="D1:D34"/>
+  </sortState>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{7326F202-ABE8-423A-B777-E0B202745E7C}" name="id" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{7E4F2EC9-C9A9-4F69-9A5A-DC9FC26A33C7}" name="Item / Módulo" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{7D843FBA-8796-467F-B00D-15647AFA9E29}" name="Descrição do Requisito" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{1E1EFF6E-C0F3-4AC4-8344-04B0CF15A742}" name="Status" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -702,702 +948,787 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.714285714285714" customWidth="1"/>
-    <col min="2" max="2" width="18.714285714285715" customWidth="1"/>
-    <col min="3" max="3" width="41.57142857142857" customWidth="1"/>
-    <col min="4" max="4" width="33.42857142857143" customWidth="1"/>
-    <col min="5" max="5" width="14.285714285714286" customWidth="1"/>
-    <col min="6" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="38.5703125" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="5" max="24" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="2" t="s">
+    <row r="31" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="2" t="s">
+    <row r="33" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="2" t="s">
+    <row r="34" spans="1:4" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="D36" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:D38">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$D2="desenvolver"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$D2="feito"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FBA40CA9-3B10-458F-8640-5B6C5F5B8856}">
+          <x14:formula1>
+            <xm:f>variaveis!$B$2:$B$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D38</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B6AD1E33-F434-47CF-A3BF-DFF229032800}">
+          <x14:formula1>
+            <xm:f>variaveis!$E$2:$E$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A38</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.857142857142858" customWidth="1"/>
-    <col min="2" max="2" width="38.57142857142857" customWidth="1"/>
-    <col min="3" max="3" width="42.142857142857146" customWidth="1"/>
-    <col min="4" max="4" width="21.285714285714285" customWidth="1"/>
-    <col min="5" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="41.5703125" customWidth="1"/>
+    <col min="4" max="4" width="33.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="24" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="3" t="s">
+    <row r="1" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="3" t="s">
+    <row r="3" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="3" t="s">
+    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="31" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="3"/>
+    <row r="5" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11" t="s">
+        <v>93</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
-    <col min="2" max="2" width="14.428571428571429" customWidth="1"/>
-    <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="24" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1472,6 +1803,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>